--- a/output/pdf_financials_xlsx/CEXY.xlsx
+++ b/output/pdf_financials_xlsx/CEXY.xlsx
@@ -2207,16 +2207,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.117862</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.988479</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.585758</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.789993</v>
       </c>
     </row>
     <row r="93">
@@ -2689,16 +2689,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-2.275214</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-2.683088</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.645689</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-2.642786</v>
       </c>
     </row>
     <row r="119">
@@ -3500,7 +3500,11 @@
           <t>Reserves (Notes 9, 10 and 11)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3750,7 +3754,11 @@
           <t>Reserves (Note 6, 7 &amp; 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>4.117862</v>
       </c>
@@ -4092,7 +4100,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4880,7 +4892,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-2.275214</v>
       </c>

--- a/output/pdf_financials_xlsx/CEXY.xlsx
+++ b/output/pdf_financials_xlsx/CEXY.xlsx
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.732623</v>
+        <v>7.887565</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.98689</v>
+        <v>4.806293</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.232937</v>
+        <v>3.131566</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5.415727</v>
+        <v>7.066234</v>
       </c>
     </row>
     <row r="11">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-3.732623</v>
+        <v>-7.887565</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.98689</v>
+        <v>-4.806293</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002442</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014507</v>
       </c>
     </row>
     <row r="13">
@@ -958,10 +958,10 @@
         <v>-5.095519</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.991883</v>
+        <v>-2.989441</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.585526</v>
+        <v>-7.571019</v>
       </c>
     </row>
     <row r="28">
@@ -996,10 +996,10 @@
         <v>-5.095519</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.991883</v>
+        <v>-2.989441</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.585526</v>
+        <v>-7.571019</v>
       </c>
     </row>
     <row r="30">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.044966</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.305339</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.707117</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.897064</v>
       </c>
     </row>
     <row r="35">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.044966</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.305339</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.707117</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.897064</v>
       </c>
     </row>
     <row r="37">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.334132</v>
+        <v>0.289166</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.426786</v>
+        <v>0.121447</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.659031</v>
+        <v>0.951914</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.639832</v>
+        <v>1.742768</v>
       </c>
     </row>
     <row r="49">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEXY.xlsx
+++ b/output/pdf_financials_xlsx/CEXY.xlsx
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.106713</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.108907</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.043945</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.000491</v>
       </c>
     </row>
     <row r="102">
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.614244</v>
+        <v>0.507531</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.025298</v>
+        <v>-0.134205</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.827659</v>
+        <v>-0.871604</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.457718</v>
+        <v>-0.457227</v>
       </c>
     </row>
     <row r="107">
@@ -3932,7 +3932,11 @@
           <t>Recovery of GST receivable</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -3968,7 +3972,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.106713</v>
       </c>
